--- a/Result/profitability/2342.xlsx
+++ b/Result/profitability/2342.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-1.17</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1625</v>
+        <v>-0.2025</v>
       </c>
       <c r="N2" t="n">
-        <v>15.26125</v>
+        <v>14.0975</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.61</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.26375</v>
+        <v>-0.31125</v>
       </c>
       <c r="N3" t="n">
-        <v>14.76875</v>
+        <v>13.76125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.76</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.39125</v>
+        <v>-0.4287500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>14.6675</v>
+        <v>13.92625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-6.84</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.26875</v>
+        <v>-1.2375</v>
       </c>
       <c r="N5" t="n">
-        <v>9.8675</v>
+        <v>9.465</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.47</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.28125</v>
+        <v>-1.2925</v>
       </c>
       <c r="N6" t="n">
-        <v>3.423749999999999</v>
+        <v>3.981249999999999</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.41</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.32875</v>
+        <v>-1.31125</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8849999999999998</v>
+        <v>1.536249999999999</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.35</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.34</v>
+        <v>-1.34125</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.03375000000000045</v>
+        <v>-0.1787500000000009</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>-1.22375</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.105</v>
+        <v>-1.105000000000001</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>-1.05125</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1962499999999996</v>
+        <v>0.1962499999999991</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>-0.8962500000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>0.08249999999999957</v>
+        <v>0.08249999999999913</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>-0.8850000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4087500000000004</v>
+        <v>-0.4087500000000008</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>-0.1912500000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>1.455</v>
+        <v>1.454999999999999</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2342</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>522</v>
+      </c>
+      <c r="D75" t="n">
+        <v>445</v>
+      </c>
+      <c r="E75" t="n">
+        <v>77</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-22</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-4.30%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-19</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-19</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.03125000000000006</v>
+      </c>
+      <c r="N75" t="n">
+        <v>16.95125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.009999999999999995</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.09090909090909083</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.07313997477931911</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.6756756756756757</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.220000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1796875000000001</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
